--- a/july 2026/LMT_JULY_26/Rainbow/Rainbow Cash & Carry Model Town.xlsx
+++ b/july 2026/LMT_JULY_26/Rainbow/Rainbow Cash & Carry Model Town.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8587CBC8-5A94-4BF3-8BA6-CBDCE293B2A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F0B7AB5-55CC-4F5D-A8B6-5D16685B2375}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3379,7 +3379,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -3407,7 +3407,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -4624,7 +4624,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -4652,7 +4652,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -5869,7 +5869,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -5897,7 +5897,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -7114,7 +7114,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -7142,7 +7142,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -8359,7 +8359,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -8387,7 +8387,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -9604,7 +9604,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -9632,7 +9632,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -10849,7 +10849,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -10877,7 +10877,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -12094,7 +12094,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -12122,7 +12122,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -13339,7 +13339,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -13367,7 +13367,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -14584,7 +14584,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -14612,7 +14612,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -18579,7 +18579,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -18607,7 +18607,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -19821,7 +19821,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -19849,7 +19849,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -21062,7 +21062,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -21090,7 +21090,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -22303,7 +22303,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -22331,7 +22331,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -23549,7 +23549,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -23577,7 +23577,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -23788,7 +23788,7 @@
       </c>
       <c r="U14" s="163">
         <f>+'1'!P35</f>
-        <v>30892.8814074</v>
+        <v>10679.162411249999</v>
       </c>
       <c r="XFD14" t="s">
         <v>75</v>
@@ -23874,15 +23874,15 @@
       <c r="G16" s="113"/>
       <c r="H16" s="171">
         <f>+'1'!H16+'2'!H16+'4'!H16+'3'!H16+'5'!H16+'6'!H16+'7'!H16+'8'!H16+'9'!H16+'10'!H16+'11'!H16+'12'!H16+'13'!H16+'14'!H16+'15'!H16+'16'!H16+'17'!H16+'18'!H16</f>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I16" s="1">
         <f>(G16*D16)*F16+H16*F16</f>
-        <v>2098.5</v>
+        <v>0</v>
       </c>
       <c r="J16" s="171">
         <f>+'1'!J16+'2'!J16+'4'!J16+'3'!J16+'5'!J16+'6'!J16+'7'!J16+'8'!J16+'9'!J16+'10'!J16+'11'!J16+'12'!J16+'13'!J16+'14'!J16+'15'!J16+'16'!J16+'17'!J16+'18'!J16</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K16" s="171">
         <f>+'1'!K16+'2'!K16+'4'!K16+'3'!K16+'5'!K16+'6'!K16+'7'!K16+'8'!K16+'9'!K16+'10'!K16</f>
@@ -23890,23 +23890,23 @@
       </c>
       <c r="L16" s="174">
         <f>+'1'!L16+'2'!L16+'4'!L16+'3'!L16+'5'!L16+'6'!L16+'7'!L16+'8'!L16+'9'!L16+'10'!L16</f>
-        <v>293.79000000000002</v>
+        <v>0</v>
       </c>
       <c r="M16" s="105">
         <f>I16-K16-L16</f>
-        <v>1804.71</v>
+        <v>0</v>
       </c>
       <c r="N16" s="100">
         <f>+'1'!N16+'2'!N16+'4'!N16+'3'!N16+'5'!N16+'6'!N16+'7'!N16+'8'!N16+'9'!N16+'10'!N16</f>
-        <v>343.73430000000002</v>
+        <v>0</v>
       </c>
       <c r="O16" s="100">
         <f>+'1'!O16+'2'!O16+'4'!O16+'3'!O16+'5'!O16+'6'!O16+'7'!O16+'8'!O16+'9'!O16+'10'!O16</f>
-        <v>10.742221500000001</v>
+        <v>0</v>
       </c>
       <c r="P16" s="104">
         <f t="shared" ref="P16:P24" si="0">M16+N16+O16</f>
-        <v>2159.1865215000003</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="107"/>
       <c r="T16" s="162" t="str">
@@ -23948,39 +23948,39 @@
       <c r="G17" s="113"/>
       <c r="H17" s="171">
         <f>+'1'!H17+'2'!H17+'4'!H17+'3'!H17+'5'!H17+'6'!H17+'7'!H17+'8'!H17+'9'!H17+'10'!H17+'11'!H17+'12'!H17+'13'!H17+'14'!H17+'15'!H17+'16'!H17+'17'!H17+'18'!H17</f>
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I17" s="1">
         <f t="shared" ref="I17:I23" si="1">(G17*D17)*F17+H17*F17</f>
-        <v>4197</v>
+        <v>2098.5</v>
       </c>
       <c r="J17" s="171">
         <f>+'1'!J17+'2'!J17+'4'!J17+'3'!J17+'5'!J17+'6'!J17+'7'!J17+'8'!J17+'9'!J17+'10'!J17+'11'!J17+'12'!J17+'13'!J17+'14'!J17+'15'!J17+'16'!J17+'17'!J17+'18'!J17</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K17" s="171">
         <f>+'1'!K17+'2'!K17+'4'!K17+'3'!K17+'5'!K17+'6'!K17+'7'!K17+'8'!K17+'9'!K17+'10'!K17</f>
-        <v>0</v>
+        <v>73.447500000000005</v>
       </c>
       <c r="L17" s="174">
         <f>+'1'!L17+'2'!L17+'4'!L17+'3'!L17+'5'!L17+'6'!L17+'7'!L17+'8'!L17+'9'!L17+'10'!L17</f>
-        <v>587.58000000000004</v>
+        <v>293.79000000000002</v>
       </c>
       <c r="M17" s="117">
         <f t="shared" ref="M17:M23" si="2">I17-K17-L17</f>
-        <v>3609.42</v>
+        <v>1731.2625</v>
       </c>
       <c r="N17" s="100">
         <f>+'1'!N17+'2'!N17+'4'!N17+'3'!N17+'5'!N17+'6'!N17+'7'!N17+'8'!N17+'9'!N17+'10'!N17</f>
-        <v>687.46860000000004</v>
+        <v>330.51375000000002</v>
       </c>
       <c r="O17" s="100">
         <f>+'1'!O17+'2'!O17+'4'!O17+'3'!O17+'5'!O17+'6'!O17+'7'!O17+'8'!O17+'9'!O17+'10'!O17</f>
-        <v>21.484443000000002</v>
+        <v>10.308881249999999</v>
       </c>
       <c r="P17" s="119">
         <f t="shared" si="0"/>
-        <v>4318.3730430000005</v>
+        <v>2072.0851312499999</v>
       </c>
       <c r="S17" s="64"/>
       <c r="T17" s="162" t="str">
@@ -24022,15 +24022,15 @@
       <c r="G18" s="113"/>
       <c r="H18" s="171">
         <f>+'1'!H18+'2'!H18+'4'!H18+'3'!H18+'5'!H18+'6'!H18+'7'!H18+'8'!H18+'9'!H18+'10'!H18+'11'!H18+'12'!H18+'13'!H18+'14'!H18+'15'!H18+'16'!H18+'17'!H18+'18'!H18</f>
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="I18" s="1">
         <f t="shared" si="1"/>
-        <v>6295.5</v>
+        <v>0</v>
       </c>
       <c r="J18" s="171">
         <f>+'1'!J18+'2'!J18+'4'!J18+'3'!J18+'5'!J18+'6'!J18+'7'!J18+'8'!J18+'9'!J18+'10'!J18+'11'!J18+'12'!J18+'13'!J18+'14'!J18+'15'!J18+'16'!J18+'17'!J18+'18'!J18</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K18" s="171">
         <f>+'1'!K18+'2'!K18+'4'!K18+'3'!K18+'5'!K18+'6'!K18+'7'!K18+'8'!K18+'9'!K18+'10'!K18</f>
@@ -24038,23 +24038,23 @@
       </c>
       <c r="L18" s="174">
         <f>+'1'!L18+'2'!L18+'4'!L18+'3'!L18+'5'!L18+'6'!L18+'7'!L18+'8'!L18+'9'!L18+'10'!L18</f>
-        <v>881.37000000000012</v>
+        <v>0</v>
       </c>
       <c r="M18" s="117">
         <f t="shared" si="2"/>
-        <v>5414.13</v>
+        <v>0</v>
       </c>
       <c r="N18" s="100">
         <f>+'1'!N18+'2'!N18+'4'!N18+'3'!N18+'5'!N18+'6'!N18+'7'!N18+'8'!N18+'9'!N18+'10'!N18</f>
-        <v>1031.2029</v>
+        <v>0</v>
       </c>
       <c r="O18" s="100">
         <f>+'1'!O18+'2'!O18+'4'!O18+'3'!O18+'5'!O18+'6'!O18+'7'!O18+'8'!O18+'9'!O18+'10'!O18</f>
-        <v>32.226664500000005</v>
+        <v>0</v>
       </c>
       <c r="P18" s="119">
         <f t="shared" si="0"/>
-        <v>6477.5595645000003</v>
+        <v>0</v>
       </c>
       <c r="T18" s="162" t="str">
         <f>+'5'!A5</f>
@@ -24092,39 +24092,39 @@
       <c r="G19" s="113"/>
       <c r="H19" s="171">
         <f>+'1'!H19+'2'!H19+'4'!H19+'3'!H19+'5'!H19+'6'!H19+'7'!H19+'8'!H19+'9'!H19+'10'!H19+'11'!H19+'12'!H19+'13'!H19+'14'!H19+'15'!H19+'16'!H19+'17'!H19+'18'!H19</f>
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I19" s="1">
         <f t="shared" si="1"/>
-        <v>5811.2</v>
+        <v>2905.6</v>
       </c>
       <c r="J19" s="171">
         <f>+'1'!J19+'2'!J19+'4'!J19+'3'!J19+'5'!J19+'6'!J19+'7'!J19+'8'!J19+'9'!J19+'10'!J19+'11'!J19+'12'!J19+'13'!J19+'14'!J19+'15'!J19+'16'!J19+'17'!J19+'18'!J19</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K19" s="171">
         <f>+'1'!K19+'2'!K19+'4'!K19+'3'!K19+'5'!K19+'6'!K19+'7'!K19+'8'!K19+'9'!K19+'10'!K19</f>
-        <v>0</v>
+        <v>101.69600000000001</v>
       </c>
       <c r="L19" s="174">
         <f>+'1'!L19+'2'!L19+'4'!L19+'3'!L19+'5'!L19+'6'!L19+'7'!L19+'8'!L19+'9'!L19+'10'!L19</f>
-        <v>813.5680000000001</v>
+        <v>406.78400000000005</v>
       </c>
       <c r="M19" s="117">
         <f t="shared" si="2"/>
-        <v>4997.6319999999996</v>
+        <v>2397.12</v>
       </c>
       <c r="N19" s="100">
         <f>+'1'!N19+'2'!N19+'4'!N19+'3'!N19+'5'!N19+'6'!N19+'7'!N19+'8'!N19+'9'!N19+'10'!N19</f>
-        <v>951.87455999999986</v>
+        <v>457.63199999999995</v>
       </c>
       <c r="O19" s="100">
         <f>+'1'!O19+'2'!O19+'4'!O19+'3'!O19+'5'!O19+'6'!O19+'7'!O19+'8'!O19+'9'!O19+'10'!O19</f>
-        <v>29.747532799999998</v>
+        <v>14.273759999999999</v>
       </c>
       <c r="P19" s="119">
         <f t="shared" si="0"/>
-        <v>5979.2540927999999</v>
+        <v>2869.02576</v>
       </c>
       <c r="T19" s="162" t="str">
         <f>+'6'!A5</f>
@@ -24162,39 +24162,39 @@
       <c r="G20" s="113"/>
       <c r="H20" s="171">
         <f>+'1'!H20+'2'!H20+'4'!H20+'3'!H20+'5'!H20+'6'!H20+'7'!H20+'8'!H20+'9'!H20+'10'!H20+'11'!H20+'12'!H20+'13'!H20+'14'!H20+'15'!H20+'16'!H20+'17'!H20+'18'!H20</f>
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I20" s="1">
         <f t="shared" si="1"/>
-        <v>5811.2</v>
+        <v>2905.6</v>
       </c>
       <c r="J20" s="171">
         <f>+'1'!J20+'2'!J20+'4'!J20+'3'!J20+'5'!J20+'6'!J20+'7'!J20+'8'!J20+'9'!J20+'10'!J20+'11'!J20+'12'!J20+'13'!J20+'14'!J20+'15'!J20+'16'!J20+'17'!J20+'18'!J20</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K20" s="171">
         <f>+'1'!K20+'2'!K20+'4'!K20+'3'!K20+'5'!K20+'6'!K20+'7'!K20+'8'!K20+'9'!K20+'10'!K20</f>
-        <v>0</v>
+        <v>101.69600000000001</v>
       </c>
       <c r="L20" s="174">
         <f>+'1'!L20+'2'!L20+'4'!L20+'3'!L20+'5'!L20+'6'!L20+'7'!L20+'8'!L20+'9'!L20+'10'!L20</f>
-        <v>813.5680000000001</v>
+        <v>406.78400000000005</v>
       </c>
       <c r="M20" s="117">
         <f t="shared" si="2"/>
-        <v>4997.6319999999996</v>
+        <v>2397.12</v>
       </c>
       <c r="N20" s="100">
         <f>+'1'!N20+'2'!N20+'4'!N20+'3'!N20+'5'!N20+'6'!N20+'7'!N20+'8'!N20+'9'!N20+'10'!N20</f>
-        <v>951.87455999999986</v>
+        <v>457.63199999999995</v>
       </c>
       <c r="O20" s="100">
         <f>+'1'!O20+'2'!O20+'4'!O20+'3'!O20+'5'!O20+'6'!O20+'7'!O20+'8'!O20+'9'!O20+'10'!O20</f>
-        <v>29.747532799999998</v>
+        <v>14.273759999999999</v>
       </c>
       <c r="P20" s="119">
         <f t="shared" si="0"/>
-        <v>5979.2540927999999</v>
+        <v>2869.02576</v>
       </c>
       <c r="T20" s="162" t="str">
         <f>+'7'!A5</f>
@@ -24232,39 +24232,39 @@
       <c r="G21" s="113"/>
       <c r="H21" s="171">
         <f>+'1'!H21+'2'!H21+'4'!H21+'3'!H21+'5'!H21+'6'!H21+'7'!H21+'8'!H21+'9'!H21+'10'!H21+'11'!H21+'12'!H21+'13'!H21+'14'!H21+'15'!H21+'16'!H21+'17'!H21+'18'!H21</f>
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I21" s="1">
         <f t="shared" si="1"/>
-        <v>5811.2</v>
+        <v>2905.6</v>
       </c>
       <c r="J21" s="171">
         <f>+'1'!J21+'2'!J21+'4'!J21+'3'!J21+'5'!J21+'6'!J21+'7'!J21+'8'!J21+'9'!J21+'10'!J21+'11'!J21+'12'!J21+'13'!J21+'14'!J21+'15'!J21+'16'!J21+'17'!J21+'18'!J21</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K21" s="171">
         <f>+'1'!K21+'2'!K21+'4'!K21+'3'!K21+'5'!K21+'6'!K21+'7'!K21+'8'!K21+'9'!K21+'10'!K21</f>
-        <v>0</v>
+        <v>101.69600000000001</v>
       </c>
       <c r="L21" s="174">
         <f>+'1'!L21+'2'!L21+'4'!L21+'3'!L21+'5'!L21+'6'!L21+'7'!L21+'8'!L21+'9'!L21+'10'!L21</f>
-        <v>813.5680000000001</v>
+        <v>406.78400000000005</v>
       </c>
       <c r="M21" s="117">
         <f t="shared" si="2"/>
-        <v>4997.6319999999996</v>
+        <v>2397.12</v>
       </c>
       <c r="N21" s="100">
         <f>+'1'!N21+'2'!N21+'4'!N21+'3'!N21+'5'!N21+'6'!N21+'7'!N21+'8'!N21+'9'!N21+'10'!N21</f>
-        <v>951.87455999999986</v>
+        <v>457.63199999999995</v>
       </c>
       <c r="O21" s="100">
         <f>+'1'!O21+'2'!O21+'4'!O21+'3'!O21+'5'!O21+'6'!O21+'7'!O21+'8'!O21+'9'!O21+'10'!O21</f>
-        <v>29.747532799999998</v>
+        <v>14.273759999999999</v>
       </c>
       <c r="P21" s="119">
         <f t="shared" si="0"/>
-        <v>5979.2540927999999</v>
+        <v>2869.02576</v>
       </c>
       <c r="T21" s="162" t="str">
         <f>+'8'!A5</f>
@@ -24492,7 +24492,7 @@
       <c r="B25" s="227"/>
       <c r="C25" s="228">
         <f>H25/40</f>
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D25" s="222"/>
       <c r="E25" s="222"/>
@@ -24503,39 +24503,39 @@
       </c>
       <c r="H25" s="176">
         <f t="shared" si="3"/>
-        <v>480</v>
+        <v>160</v>
       </c>
       <c r="I25" s="177">
         <f t="shared" si="3"/>
-        <v>30024.600000000002</v>
+        <v>10815.300000000001</v>
       </c>
       <c r="J25" s="176">
         <f t="shared" si="3"/>
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="K25" s="177">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>378.53550000000007</v>
       </c>
       <c r="L25" s="178">
         <f t="shared" si="3"/>
-        <v>4203.4440000000004</v>
+        <v>1514.1420000000003</v>
       </c>
       <c r="M25" s="140">
         <f t="shared" si="3"/>
-        <v>25821.155999999995</v>
+        <v>8922.6224999999995</v>
       </c>
       <c r="N25" s="141">
         <f>SUM(N16:N24)</f>
-        <v>4918.0294799999992</v>
+        <v>1703.4097499999998</v>
       </c>
       <c r="O25" s="142">
         <f>SUM(O16:O24)</f>
-        <v>153.69592740000002</v>
+        <v>53.13016125</v>
       </c>
       <c r="P25" s="143">
         <f>SUM(P16:P24)</f>
-        <v>30892.881407400004</v>
+        <v>10679.162411250001</v>
       </c>
       <c r="T25" s="162" t="str">
         <f>+'12'!A5</f>
@@ -24743,7 +24743,7 @@
       </c>
       <c r="U33" s="164">
         <f>SUM(U14:U28)</f>
-        <v>30892.8814074</v>
+        <v>10679.162411249999</v>
       </c>
     </row>
     <row r="34" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -24776,7 +24776,7 @@
       <c r="O35" s="239"/>
       <c r="P35" s="151">
         <f>I25</f>
-        <v>30024.600000000002</v>
+        <v>10815.300000000001</v>
       </c>
     </row>
     <row r="36" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24797,7 +24797,7 @@
       <c r="O36" s="241"/>
       <c r="P36" s="152">
         <f>L25</f>
-        <v>4203.4440000000004</v>
+        <v>1514.1420000000003</v>
       </c>
     </row>
     <row r="37" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24818,7 +24818,7 @@
       <c r="O37" s="241"/>
       <c r="P37" s="153">
         <f>K25</f>
-        <v>0</v>
+        <v>378.53550000000007</v>
       </c>
     </row>
     <row r="38" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24840,7 +24840,7 @@
       <c r="O38" s="241"/>
       <c r="P38" s="152">
         <f>P35-P36-P37</f>
-        <v>25821.156000000003</v>
+        <v>8922.6225000000013</v>
       </c>
     </row>
     <row r="39" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24865,7 +24865,7 @@
       </c>
       <c r="P39" s="152">
         <f>N25</f>
-        <v>4918.0294799999992</v>
+        <v>1703.4097499999998</v>
       </c>
     </row>
     <row r="40" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24887,7 +24887,7 @@
       <c r="O40" s="243"/>
       <c r="P40" s="152">
         <f>P38+P39</f>
-        <v>30739.18548</v>
+        <v>10626.03225</v>
       </c>
     </row>
     <row r="41" spans="1:21" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24912,7 +24912,7 @@
       </c>
       <c r="P41" s="152">
         <f>O41*P40</f>
-        <v>768.47963700000003</v>
+        <v>265.65080625000002</v>
       </c>
     </row>
     <row r="42" spans="1:21" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24922,7 +24922,7 @@
       <c r="O42" s="221"/>
       <c r="P42" s="159">
         <f>P40+P41</f>
-        <v>31507.665117</v>
+        <v>10891.68305625</v>
       </c>
     </row>
     <row r="43" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -25094,7 +25094,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -25122,7 +25122,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -25414,39 +25414,35 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G16" s="99"/>
-      <c r="H16" s="100">
-        <v>40</v>
-      </c>
+      <c r="H16" s="100"/>
       <c r="I16" s="101">
         <f>(G16*D16)*F16+H16*F16</f>
-        <v>2098.5</v>
-      </c>
-      <c r="J16" s="102">
-        <v>2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J16" s="102"/>
       <c r="K16" s="103">
-        <f>I16*$K$13</f>
+        <f>I16*3.5%</f>
         <v>0</v>
       </c>
       <c r="L16" s="104">
         <f>I16*14%</f>
-        <v>293.79000000000002</v>
+        <v>0</v>
       </c>
       <c r="M16" s="105">
         <f>I16-K16-L16</f>
-        <v>1804.71</v>
+        <v>0</v>
       </c>
       <c r="N16" s="105">
         <f t="shared" ref="N16:N24" si="0">(M16*$N$15)+(J16*F16)*$N$15</f>
-        <v>343.73430000000002</v>
+        <v>0</v>
       </c>
       <c r="O16" s="106">
         <f t="shared" ref="O16:O24" si="1">(N16+M16)*$O$15</f>
-        <v>10.742221500000001</v>
+        <v>0</v>
       </c>
       <c r="P16" s="104">
         <f t="shared" ref="P16:P24" si="2">M16+N16+O16</f>
-        <v>2159.1865215000003</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="107"/>
       <c r="XFD16" t="s">
@@ -25479,38 +25475,38 @@
       </c>
       <c r="G17" s="113"/>
       <c r="H17" s="114">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I17" s="115">
         <f t="shared" ref="I17:I23" si="3">(G17*D17)*F17+H17*F17</f>
-        <v>4197</v>
+        <v>2098.5</v>
       </c>
       <c r="J17" s="116">
-        <v>4</v>
-      </c>
-      <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="4">I17*$K$13</f>
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="K17" s="103">
+        <f t="shared" ref="K17:K22" si="4">I17*3.5%</f>
+        <v>73.447500000000005</v>
       </c>
       <c r="L17" s="104">
         <f t="shared" ref="L17:L21" si="5">I17*14%</f>
-        <v>587.58000000000004</v>
+        <v>293.79000000000002</v>
       </c>
       <c r="M17" s="117">
         <f t="shared" ref="M17:M23" si="6">I17-K17-L17</f>
-        <v>3609.42</v>
+        <v>1731.2625</v>
       </c>
       <c r="N17" s="117">
         <f t="shared" si="0"/>
-        <v>687.46860000000004</v>
+        <v>330.51375000000002</v>
       </c>
       <c r="O17" s="118">
         <f t="shared" si="1"/>
-        <v>21.484443000000002</v>
+        <v>10.308881249999999</v>
       </c>
       <c r="P17" s="119">
         <f t="shared" si="2"/>
-        <v>4318.3730430000005</v>
+        <v>2072.0851312499999</v>
       </c>
       <c r="S17" s="64"/>
       <c r="XFD17" t="s">
@@ -25542,39 +25538,35 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G18" s="113"/>
-      <c r="H18" s="114">
-        <v>120</v>
-      </c>
+      <c r="H18" s="114"/>
       <c r="I18" s="115">
         <f t="shared" si="3"/>
-        <v>6295.5</v>
-      </c>
-      <c r="J18" s="116">
-        <v>6</v>
-      </c>
-      <c r="K18" s="1">
+        <v>0</v>
+      </c>
+      <c r="J18" s="116"/>
+      <c r="K18" s="103">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L18" s="104">
         <f t="shared" si="5"/>
-        <v>881.37000000000012</v>
+        <v>0</v>
       </c>
       <c r="M18" s="117">
         <f t="shared" si="6"/>
-        <v>5414.13</v>
+        <v>0</v>
       </c>
       <c r="N18" s="117">
         <f t="shared" si="0"/>
-        <v>1031.2029</v>
+        <v>0</v>
       </c>
       <c r="O18" s="118">
         <f t="shared" si="1"/>
-        <v>32.226664500000005</v>
+        <v>0</v>
       </c>
       <c r="P18" s="119">
         <f t="shared" si="2"/>
-        <v>6477.5595645000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -25603,38 +25595,38 @@
       </c>
       <c r="G19" s="113"/>
       <c r="H19" s="114">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I19" s="115">
         <f t="shared" si="3"/>
-        <v>5811.2</v>
+        <v>2905.6</v>
       </c>
       <c r="J19" s="116">
-        <v>4</v>
-      </c>
-      <c r="K19" s="1">
+        <v>2</v>
+      </c>
+      <c r="K19" s="103">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>101.69600000000001</v>
       </c>
       <c r="L19" s="104">
         <f t="shared" si="5"/>
-        <v>813.5680000000001</v>
+        <v>406.78400000000005</v>
       </c>
       <c r="M19" s="117">
         <f t="shared" si="6"/>
-        <v>4997.6319999999996</v>
+        <v>2397.12</v>
       </c>
       <c r="N19" s="117">
         <f t="shared" si="0"/>
-        <v>951.87455999999986</v>
+        <v>457.63199999999995</v>
       </c>
       <c r="O19" s="118">
         <f t="shared" si="1"/>
-        <v>29.747532799999998</v>
+        <v>14.273759999999999</v>
       </c>
       <c r="P19" s="119">
         <f t="shared" si="2"/>
-        <v>5979.2540927999999</v>
+        <v>2869.02576</v>
       </c>
     </row>
     <row r="20" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -25663,38 +25655,38 @@
       </c>
       <c r="G20" s="113"/>
       <c r="H20" s="114">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I20" s="115">
         <f t="shared" si="3"/>
-        <v>5811.2</v>
+        <v>2905.6</v>
       </c>
       <c r="J20" s="116">
-        <v>4</v>
-      </c>
-      <c r="K20" s="1">
+        <v>2</v>
+      </c>
+      <c r="K20" s="103">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>101.69600000000001</v>
       </c>
       <c r="L20" s="104">
         <f t="shared" si="5"/>
-        <v>813.5680000000001</v>
+        <v>406.78400000000005</v>
       </c>
       <c r="M20" s="117">
         <f t="shared" si="6"/>
-        <v>4997.6319999999996</v>
+        <v>2397.12</v>
       </c>
       <c r="N20" s="117">
         <f t="shared" si="0"/>
-        <v>951.87455999999986</v>
+        <v>457.63199999999995</v>
       </c>
       <c r="O20" s="118">
         <f t="shared" si="1"/>
-        <v>29.747532799999998</v>
+        <v>14.273759999999999</v>
       </c>
       <c r="P20" s="119">
         <f t="shared" si="2"/>
-        <v>5979.2540927999999</v>
+        <v>2869.02576</v>
       </c>
     </row>
     <row r="21" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -25723,38 +25715,38 @@
       </c>
       <c r="G21" s="113"/>
       <c r="H21" s="114">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="I21" s="115">
         <f t="shared" si="3"/>
-        <v>5811.2</v>
+        <v>2905.6</v>
       </c>
       <c r="J21" s="116">
-        <v>4</v>
-      </c>
-      <c r="K21" s="1">
+        <v>2</v>
+      </c>
+      <c r="K21" s="103">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>101.69600000000001</v>
       </c>
       <c r="L21" s="104">
         <f t="shared" si="5"/>
-        <v>813.5680000000001</v>
+        <v>406.78400000000005</v>
       </c>
       <c r="M21" s="117">
         <f t="shared" si="6"/>
-        <v>4997.6319999999996</v>
+        <v>2397.12</v>
       </c>
       <c r="N21" s="117">
         <f t="shared" si="0"/>
-        <v>951.87455999999986</v>
+        <v>457.63199999999995</v>
       </c>
       <c r="O21" s="118">
         <f t="shared" si="1"/>
-        <v>29.747532799999998</v>
+        <v>14.273759999999999</v>
       </c>
       <c r="P21" s="119">
         <f t="shared" si="2"/>
-        <v>5979.2540927999999</v>
+        <v>2869.02576</v>
       </c>
     </row>
     <row r="22" spans="1:19 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -25782,16 +25774,14 @@
         <v>39.230000000000004</v>
       </c>
       <c r="G22" s="113"/>
-      <c r="H22" s="114">
-        <v>0</v>
-      </c>
+      <c r="H22" s="114"/>
       <c r="I22" s="115">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="J22" s="116"/>
-      <c r="K22" s="1">
-        <f>I22*3.5%</f>
+      <c r="K22" s="103">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="L22" s="119">
@@ -25942,39 +25932,39 @@
       </c>
       <c r="H25" s="135">
         <f t="shared" si="9"/>
-        <v>480</v>
+        <v>160</v>
       </c>
       <c r="I25" s="136">
         <f t="shared" si="9"/>
-        <v>30024.600000000002</v>
+        <v>10815.300000000001</v>
       </c>
       <c r="J25" s="182">
         <f>SUM(J16:J21)</f>
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="K25" s="138">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>378.53550000000007</v>
       </c>
       <c r="L25" s="139">
         <f t="shared" si="9"/>
-        <v>4203.4440000000004</v>
+        <v>1514.1420000000003</v>
       </c>
       <c r="M25" s="140">
         <f t="shared" si="9"/>
-        <v>25821.155999999995</v>
+        <v>8922.6224999999995</v>
       </c>
       <c r="N25" s="141">
         <f>SUM(N16:N24)</f>
-        <v>4918.0294799999992</v>
+        <v>1703.4097499999998</v>
       </c>
       <c r="O25" s="142">
         <f>SUM(O16:O24)</f>
-        <v>153.69592740000002</v>
+        <v>53.13016125</v>
       </c>
       <c r="P25" s="143">
         <f>SUM(P16:P24)</f>
-        <v>30892.881407400004</v>
+        <v>10679.162411250001</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -26024,7 +26014,7 @@
       <c r="O28" s="239"/>
       <c r="P28" s="151">
         <f>I25</f>
-        <v>30024.600000000002</v>
+        <v>10815.300000000001</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26045,7 +26035,7 @@
       <c r="O29" s="241"/>
       <c r="P29" s="152">
         <f>L25</f>
-        <v>4203.4440000000004</v>
+        <v>1514.1420000000003</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26066,7 +26056,7 @@
       <c r="O30" s="241"/>
       <c r="P30" s="153">
         <f>K25</f>
-        <v>0</v>
+        <v>378.53550000000007</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26088,7 +26078,7 @@
       <c r="O31" s="241"/>
       <c r="P31" s="152">
         <f>P28-P29-P30</f>
-        <v>25821.156000000003</v>
+        <v>8922.6225000000013</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26113,7 +26103,7 @@
       </c>
       <c r="P32" s="152">
         <f>N25</f>
-        <v>4918.0294799999992</v>
+        <v>1703.4097499999998</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26135,7 +26125,7 @@
       <c r="O33" s="243"/>
       <c r="P33" s="152">
         <f>P31+P32</f>
-        <v>30739.18548</v>
+        <v>10626.03225</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -26160,7 +26150,7 @@
       </c>
       <c r="P34" s="152">
         <f>O34*P33</f>
-        <v>153.69592740000002</v>
+        <v>53.13016125</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -26170,7 +26160,7 @@
       <c r="O35" s="221"/>
       <c r="P35" s="159">
         <f>P33+P34</f>
-        <v>30892.8814074</v>
+        <v>10679.162411249999</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -26342,7 +26332,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -26370,7 +26360,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -27587,7 +27577,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -27615,7 +27605,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -28831,7 +28821,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -28859,7 +28849,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -30076,7 +30066,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -30104,7 +30094,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
@@ -31322,7 +31312,7 @@
       <c r="M4" s="202"/>
       <c r="N4" s="203">
         <f ca="1">TODAY()</f>
-        <v>46197</v>
+        <v>46206</v>
       </c>
       <c r="O4" s="203"/>
       <c r="P4" s="203"/>
@@ -31350,7 +31340,7 @@
       <c r="M5" s="202"/>
       <c r="N5" s="203">
         <f ca="1">N4-1</f>
-        <v>46196</v>
+        <v>46205</v>
       </c>
       <c r="O5" s="201"/>
       <c r="P5" s="201"/>
